--- a/input/timetable/Программная инженерия_.xlsx
+++ b/input/timetable/Программная инженерия_.xlsx
@@ -354,9 +354,6 @@
   </si>
   <si>
     <t>Технологии искусственного интеллекта (лек), У903//</t>
-  </si>
-  <si>
-    <t>Иностранный язык, п/г 2, А502</t>
   </si>
   <si>
     <t>Адаптивная верстка с использов. HTML5 и CSS3 , п/г 1, У504</t>
@@ -596,15 +593,6 @@
     <t>02.02.2026-28.03.2026</t>
   </si>
   <si>
-    <t>Системный подход и системное мышление (лек)/(лаб), У903/У605</t>
-  </si>
-  <si>
-    <t>Системный подход и системное мышление (лаб), У605</t>
-  </si>
-  <si>
-    <t>Системный подход и системное мышление (лаб), У605//</t>
-  </si>
-  <si>
     <t>WEB-программирование, п/г 2, ЭОиДОТ//</t>
   </si>
   <si>
@@ -624,6 +612,18 @@
   </si>
   <si>
     <t>Backend разработка, п/г 1, ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Иностранный язык, п/г 2, У505</t>
+  </si>
+  <si>
+    <t>Системный подход и системное мышление (лек)/(лаб), У903/У503,605</t>
+  </si>
+  <si>
+    <t>Системный подход и системное мышление (лаб), У503,605</t>
+  </si>
+  <si>
+    <t>Системный подход и системное мышление (лаб), У503,605//</t>
   </si>
 </sst>
 </file>
@@ -1763,6 +1763,21 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1847,6 +1862,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1909,21 +1930,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1940,15 +1949,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2761,21 +2761,21 @@
       <c r="A8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="124" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
+      <c r="C8" s="131" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
       <c r="G8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="124" t="s">
-        <v>139</v>
-      </c>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
+      <c r="I8" s="131" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
@@ -2810,88 +2810,88 @@
       <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="137"/>
-      <c r="D10" s="138"/>
-      <c r="E10" s="139" t="s">
+      <c r="C10" s="144"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="146" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="140"/>
+      <c r="F10" s="147"/>
       <c r="G10" s="24" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="25">
         <v>1</v>
       </c>
-      <c r="I10" s="137"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="145"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="151"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="26"/>
       <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="128" t="s">
+      <c r="C11" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="130"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="137"/>
       <c r="G11" s="26"/>
       <c r="H11" s="27">
         <v>2</v>
       </c>
-      <c r="I11" s="128" t="s">
+      <c r="I11" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="130"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="137"/>
     </row>
     <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
       <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="128" t="s">
+      <c r="C12" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="137"/>
       <c r="G12" s="26"/>
       <c r="H12" s="27">
         <v>3</v>
       </c>
-      <c r="I12" s="128" t="s">
+      <c r="I12" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="130"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="137"/>
     </row>
     <row r="13" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="149" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="151"/>
+      <c r="C13" s="152" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="154"/>
       <c r="G13" s="26"/>
       <c r="H13" s="27">
         <v>4</v>
       </c>
-      <c r="I13" s="131" t="s">
-        <v>153</v>
-      </c>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="133"/>
+      <c r="I13" s="138" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="139"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="140"/>
     </row>
     <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
@@ -2900,36 +2900,36 @@
       <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="127"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="134"/>
       <c r="G14" s="30" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="31">
         <v>1</v>
       </c>
-      <c r="I14" s="146" t="s">
+      <c r="I14" s="128" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="148"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="91"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="128" t="s">
+      <c r="C15" s="135" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="130"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="137"/>
       <c r="G15" s="26"/>
       <c r="H15" s="27">
         <v>2</v>
@@ -2946,12 +2946,12 @@
       <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="141" t="s">
+      <c r="C16" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="143"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="150"/>
       <c r="G16" s="26"/>
       <c r="H16" s="27">
         <v>3</v>
@@ -2959,8 +2959,8 @@
       <c r="I16" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="90"/>
-      <c r="K16" s="144" t="s">
+      <c r="J16" s="95"/>
+      <c r="K16" s="127" t="s">
         <v>101</v>
       </c>
       <c r="L16" s="80"/>
@@ -2992,24 +2992,24 @@
       <c r="B18" s="31">
         <v>1</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147" t="s">
+      <c r="D18" s="90"/>
+      <c r="E18" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="148"/>
+      <c r="F18" s="91"/>
       <c r="G18" s="30" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="31">
         <v>1</v>
       </c>
-      <c r="I18" s="115"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="117"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="122"/>
     </row>
     <row r="19" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
@@ -3028,12 +3028,12 @@
       <c r="H19" s="27">
         <v>2</v>
       </c>
-      <c r="I19" s="131" t="s">
+      <c r="I19" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="132"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="133"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="140"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
@@ -3062,40 +3062,40 @@
       <c r="B21" s="27">
         <v>4</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="26"/>
       <c r="H21" s="27">
         <v>4</v>
       </c>
-      <c r="I21" s="94"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="96"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="101"/>
     </row>
     <row r="22" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="32"/>
       <c r="B22" s="29">
         <v>7</v>
       </c>
-      <c r="C22" s="155" t="s">
+      <c r="C22" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="157"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="94"/>
       <c r="G22" s="32"/>
       <c r="H22" s="29">
         <v>7</v>
       </c>
-      <c r="I22" s="155" t="s">
+      <c r="I22" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="J22" s="156"/>
-      <c r="K22" s="156"/>
-      <c r="L22" s="157"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="94"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="30" t="s">
@@ -3104,26 +3104,26 @@
       <c r="B23" s="31">
         <v>1</v>
       </c>
-      <c r="C23" s="134" t="s">
+      <c r="C23" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="136"/>
+      <c r="D23" s="142"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="143"/>
       <c r="G23" s="30" t="s">
         <v>22</v>
       </c>
       <c r="H23" s="31">
         <v>1</v>
       </c>
-      <c r="I23" s="118" t="s">
+      <c r="I23" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="J23" s="119"/>
-      <c r="K23" s="120" t="s">
+      <c r="J23" s="124"/>
+      <c r="K23" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="L23" s="121"/>
+      <c r="L23" s="126"/>
     </row>
     <row r="24" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
@@ -3133,8 +3133,8 @@
       <c r="C24" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="144" t="s">
+      <c r="D24" s="95"/>
+      <c r="E24" s="127" t="s">
         <v>96</v>
       </c>
       <c r="F24" s="80"/>
@@ -3142,52 +3142,52 @@
       <c r="H24" s="27">
         <v>2</v>
       </c>
-      <c r="I24" s="131" t="s">
+      <c r="I24" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="J24" s="132"/>
-      <c r="K24" s="132"/>
-      <c r="L24" s="133"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="140"/>
     </row>
     <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="26"/>
       <c r="B25" s="27">
         <v>3</v>
       </c>
-      <c r="C25" s="152"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="154"/>
+      <c r="C25" s="155"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="157"/>
       <c r="G25" s="26"/>
       <c r="H25" s="27">
         <v>3</v>
       </c>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="105"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="110"/>
     </row>
     <row r="26" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="32"/>
       <c r="B26" s="29">
         <v>7</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="113"/>
       <c r="G26" s="32"/>
       <c r="H26" s="29">
         <v>7</v>
       </c>
-      <c r="I26" s="106" t="s">
+      <c r="I26" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="108"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="113"/>
     </row>
     <row r="27" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
@@ -3196,40 +3196,40 @@
       <c r="B27" s="31">
         <v>2</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="117"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="121"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="122"/>
       <c r="G27" s="30" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="31">
         <v>2</v>
       </c>
-      <c r="I27" s="100" t="s">
+      <c r="I27" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="L27" s="102"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" s="107"/>
     </row>
     <row r="28" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="26"/>
       <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C28" s="109"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="111"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="116"/>
       <c r="G28" s="26"/>
       <c r="H28" s="38">
         <v>3</v>
       </c>
       <c r="I28" s="72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J28" s="73"/>
       <c r="K28" s="73" t="s">
@@ -3246,14 +3246,14 @@
         <v>97</v>
       </c>
       <c r="D29" s="76"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="111"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="26"/>
       <c r="H29" s="38">
         <v>4</v>
       </c>
       <c r="I29" s="78" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J29" s="79"/>
       <c r="K29" s="79"/>
@@ -3265,7 +3265,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D30" s="76"/>
       <c r="E30" s="76"/>
@@ -3275,7 +3275,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="72" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J30" s="73"/>
       <c r="K30" s="73"/>
@@ -3320,12 +3320,12 @@
       <c r="H32" s="31">
         <v>2</v>
       </c>
-      <c r="I32" s="112" t="s">
+      <c r="I32" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="J32" s="113"/>
-      <c r="K32" s="113"/>
-      <c r="L32" s="114"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="119"/>
     </row>
     <row r="33" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="37"/>
@@ -3333,7 +3333,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="78" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D33" s="79"/>
       <c r="E33" s="79"/>
@@ -3356,10 +3356,10 @@
       <c r="B34" s="27">
         <v>3</v>
       </c>
-      <c r="C34" s="131"/>
-      <c r="D34" s="132"/>
-      <c r="E34" s="132"/>
-      <c r="F34" s="133"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="140"/>
       <c r="G34" s="37"/>
       <c r="H34" s="27">
         <v>5</v>
@@ -3392,60 +3392,60 @@
     <row r="36" spans="1:12" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="49"/>
       <c r="B36" s="50"/>
-      <c r="C36" s="97"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="99"/>
+      <c r="C36" s="102"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="104"/>
       <c r="G36" s="49"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="92"/>
-      <c r="L36" s="93"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="98"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="53"/>
       <c r="B37" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="123" t="s">
+      <c r="C37" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
+      <c r="D37" s="130"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
       <c r="G37" s="53"/>
       <c r="H37" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="123" t="s">
+      <c r="I37" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="123"/>
-      <c r="K37" s="123"/>
-      <c r="L37" s="123"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="130"/>
+      <c r="L37" s="130"/>
     </row>
     <row r="38" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="67"/>
       <c r="B38" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="122" t="s">
+      <c r="C38" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="122"/>
-      <c r="E38" s="122"/>
-      <c r="F38" s="122"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="129"/>
       <c r="G38" s="67"/>
       <c r="H38" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="122" t="s">
+      <c r="I38" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="J38" s="122"/>
-      <c r="K38" s="122"/>
-      <c r="L38" s="122"/>
+      <c r="J38" s="129"/>
+      <c r="K38" s="129"/>
+      <c r="L38" s="129"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
@@ -3466,13 +3466,13 @@
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3745,21 +3745,21 @@
       <c r="A8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="124" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
+      <c r="C8" s="131" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
       <c r="G8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="124" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
+      <c r="I8" s="131" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
@@ -3794,40 +3794,40 @@
       <c r="B10" s="31">
         <v>2</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120" t="s">
+      <c r="D10" s="124"/>
+      <c r="E10" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="121"/>
+      <c r="F10" s="126"/>
       <c r="G10" s="24" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="31">
         <v>1</v>
       </c>
-      <c r="I10" s="118" t="s">
+      <c r="I10" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="119"/>
-      <c r="K10" s="120" t="s">
+      <c r="J10" s="124"/>
+      <c r="K10" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="L10" s="121"/>
+      <c r="L10" s="126"/>
     </row>
     <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26"/>
       <c r="B11" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="131" t="s">
+      <c r="C11" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="133"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="140"/>
       <c r="G11" s="26"/>
       <c r="H11" s="27">
         <v>2</v>
@@ -3866,7 +3866,7 @@
       <c r="B13" s="29">
         <v>8</v>
       </c>
-      <c r="C13" s="149" t="s">
+      <c r="C13" s="152" t="s">
         <v>102</v>
       </c>
       <c r="D13" s="180"/>
@@ -3890,36 +3890,36 @@
       <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
       <c r="G14" s="30" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="31">
         <v>1</v>
       </c>
-      <c r="I14" s="146" t="s">
+      <c r="I14" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147" t="s">
+      <c r="J14" s="90"/>
+      <c r="K14" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="L14" s="148"/>
+      <c r="L14" s="91"/>
     </row>
     <row r="15" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="131" t="s">
+      <c r="C15" s="138" t="s">
         <v>79</v>
       </c>
       <c r="D15" s="182"/>
       <c r="E15" s="183"/>
-      <c r="F15" s="96"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="26"/>
       <c r="H15" s="27">
         <v>2</v>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="J15" s="185"/>
       <c r="K15" s="185" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="L15" s="186"/>
     </row>
@@ -3960,26 +3960,26 @@
       <c r="B17" s="29">
         <v>4</v>
       </c>
-      <c r="C17" s="155" t="s">
+      <c r="C17" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156" t="s">
+      <c r="D17" s="93"/>
+      <c r="E17" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="157"/>
+      <c r="F17" s="94"/>
       <c r="G17" s="32"/>
       <c r="H17" s="29">
         <v>4</v>
       </c>
-      <c r="I17" s="155" t="s">
+      <c r="I17" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="156"/>
-      <c r="K17" s="156" t="s">
+      <c r="J17" s="93"/>
+      <c r="K17" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="L17" s="157"/>
+      <c r="L17" s="94"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
@@ -4057,17 +4057,17 @@
       <c r="C21" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="90"/>
-      <c r="E21" s="144" t="s">
+      <c r="D21" s="95"/>
+      <c r="E21" s="127" t="s">
         <v>69</v>
       </c>
       <c r="F21" s="80"/>
       <c r="G21" s="42"/>
       <c r="H21" s="43"/>
-      <c r="I21" s="152"/>
+      <c r="I21" s="155"/>
       <c r="J21" s="201"/>
       <c r="K21" s="202"/>
-      <c r="L21" s="154"/>
+      <c r="L21" s="157"/>
     </row>
     <row r="22" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="42"/>
@@ -4096,22 +4096,22 @@
       <c r="B23" s="29">
         <v>7</v>
       </c>
-      <c r="C23" s="149" t="s">
+      <c r="C23" s="152" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="150"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="151"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="154"/>
       <c r="G23" s="32"/>
       <c r="H23" s="71">
         <v>7</v>
       </c>
-      <c r="I23" s="149" t="s">
+      <c r="I23" s="152" t="s">
         <v>106</v>
       </c>
-      <c r="J23" s="150"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="151"/>
+      <c r="J23" s="153"/>
+      <c r="K23" s="153"/>
+      <c r="L23" s="154"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="30" t="s">
@@ -4120,22 +4120,22 @@
       <c r="B24" s="31">
         <v>1</v>
       </c>
-      <c r="C24" s="137"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="145"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="151"/>
       <c r="G24" s="30" t="s">
         <v>22</v>
       </c>
       <c r="H24" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="I24" s="118" t="s">
+      <c r="I24" s="123" t="s">
         <v>56</v>
       </c>
       <c r="J24" s="200"/>
       <c r="K24" s="200"/>
-      <c r="L24" s="121"/>
+      <c r="L24" s="126"/>
     </row>
     <row r="25" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="26"/>
@@ -4155,9 +4155,9 @@
       <c r="I25" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="90"/>
-      <c r="K25" s="144" t="s">
-        <v>148</v>
+      <c r="J25" s="95"/>
+      <c r="K25" s="127" t="s">
+        <v>144</v>
       </c>
       <c r="L25" s="80"/>
     </row>
@@ -4166,10 +4166,10 @@
       <c r="B26" s="27">
         <v>3</v>
       </c>
-      <c r="C26" s="103"/>
-      <c r="D26" s="104"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="109"/>
       <c r="E26" s="73" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="F26" s="74"/>
       <c r="G26" s="26"/>
@@ -4177,7 +4177,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="75" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J26" s="76"/>
       <c r="K26" s="76" t="s">
@@ -4210,20 +4210,20 @@
       <c r="B28" s="31">
         <v>2</v>
       </c>
-      <c r="C28" s="137"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="145"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="151"/>
       <c r="G28" s="30" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="31">
         <v>2</v>
       </c>
-      <c r="I28" s="115"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="117"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="122"/>
     </row>
     <row r="29" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33"/>
@@ -4242,30 +4242,30 @@
       <c r="H29" s="27">
         <v>3</v>
       </c>
-      <c r="I29" s="103"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="105"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="110"/>
     </row>
     <row r="30" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="33"/>
       <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C30" s="131" t="s">
+      <c r="C30" s="138" t="s">
         <v>45</v>
       </c>
       <c r="D30" s="182"/>
       <c r="E30" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="133"/>
+      <c r="F30" s="140"/>
       <c r="G30" s="33"/>
       <c r="H30" s="27">
         <v>4</v>
       </c>
       <c r="I30" s="72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J30" s="73"/>
       <c r="K30" s="73"/>
@@ -4276,12 +4276,12 @@
       <c r="B31" s="43">
         <v>5</v>
       </c>
-      <c r="C31" s="131" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="132"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="133"/>
+      <c r="C31" s="138" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="140"/>
       <c r="G31" s="64"/>
       <c r="H31" s="43">
         <v>5</v>
@@ -4310,12 +4310,12 @@
       <c r="H32" s="43">
         <v>6</v>
       </c>
-      <c r="I32" s="155" t="s">
+      <c r="I32" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="94"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="47" t="s">
@@ -4324,24 +4324,24 @@
       <c r="B33" s="31">
         <v>1</v>
       </c>
-      <c r="C33" s="134" t="s">
+      <c r="C33" s="141" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="136"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="143"/>
       <c r="G33" s="47" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="31">
         <v>1</v>
       </c>
-      <c r="I33" s="134" t="s">
+      <c r="I33" s="141" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="135"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="136"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="142"/>
+      <c r="L33" s="143"/>
     </row>
     <row r="34" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="37"/>
@@ -4370,18 +4370,18 @@
       <c r="B35" s="43">
         <v>3</v>
       </c>
-      <c r="C35" s="152"/>
-      <c r="D35" s="153"/>
-      <c r="E35" s="153"/>
-      <c r="F35" s="154"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="157"/>
       <c r="G35" s="44"/>
       <c r="H35" s="43">
         <v>3</v>
       </c>
-      <c r="I35" s="152"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="153"/>
-      <c r="L35" s="154"/>
+      <c r="I35" s="155"/>
+      <c r="J35" s="156"/>
+      <c r="K35" s="156"/>
+      <c r="L35" s="157"/>
     </row>
     <row r="36" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="44"/>
@@ -4478,13 +4478,13 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4771,21 +4771,21 @@
       <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="124" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
+      <c r="C8" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
       <c r="G8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="124" t="s">
-        <v>143</v>
-      </c>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
+      <c r="I8" s="131" t="s">
+        <v>142</v>
+      </c>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
@@ -4821,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="252" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D10" s="253"/>
       <c r="E10" s="254"/>
@@ -4855,7 +4855,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="187" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J11" s="259"/>
       <c r="K11" s="259"/>
@@ -4879,7 +4879,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="187" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J12" s="259"/>
       <c r="K12" s="259"/>
@@ -4891,7 +4891,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="231" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D13" s="232"/>
       <c r="E13" s="232"/>
@@ -4901,7 +4901,7 @@
         <v>4</v>
       </c>
       <c r="I13" s="256" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J13" s="257"/>
       <c r="K13" s="257"/>
@@ -4935,7 +4935,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D15" s="76"/>
       <c r="E15" s="76"/>
@@ -4955,22 +4955,22 @@
       <c r="B16" s="27">
         <v>4</v>
       </c>
-      <c r="C16" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="133"/>
+      <c r="C16" s="138" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="140"/>
       <c r="G16" s="26"/>
       <c r="H16" s="27">
         <v>4</v>
       </c>
-      <c r="I16" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="132"/>
-      <c r="K16" s="132"/>
-      <c r="L16" s="133"/>
+      <c r="I16" s="138" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="140"/>
     </row>
     <row r="17" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32"/>
@@ -5009,12 +5009,12 @@
       <c r="H18" s="31">
         <v>3</v>
       </c>
-      <c r="I18" s="118" t="s">
-        <v>117</v>
+      <c r="I18" s="123" t="s">
+        <v>116</v>
       </c>
       <c r="J18" s="200"/>
       <c r="K18" s="200"/>
-      <c r="L18" s="121"/>
+      <c r="L18" s="126"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
@@ -5085,40 +5085,40 @@
       <c r="B22" s="61">
         <v>2</v>
       </c>
-      <c r="C22" s="115"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="117"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="122"/>
       <c r="G22" s="58" t="s">
         <v>22</v>
       </c>
       <c r="H22" s="61">
         <v>2</v>
       </c>
-      <c r="I22" s="146" t="s">
+      <c r="I22" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="J22" s="147"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="148"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="91"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="59"/>
       <c r="B23" s="62">
         <v>3</v>
       </c>
-      <c r="C23" s="131" t="s">
+      <c r="C23" s="138" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="133"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="140"/>
       <c r="G23" s="59"/>
       <c r="H23" s="62">
         <v>3</v>
       </c>
       <c r="I23" s="75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J23" s="76"/>
       <c r="K23" s="76"/>
@@ -5130,7 +5130,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" s="79"/>
       <c r="E24" s="79"/>
@@ -5140,7 +5140,7 @@
         <v>4</v>
       </c>
       <c r="I24" s="78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J24" s="79"/>
       <c r="K24" s="79"/>
@@ -5151,12 +5151,12 @@
       <c r="B25" s="63">
         <v>5</v>
       </c>
-      <c r="C25" s="149" t="s">
-        <v>136</v>
-      </c>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="151"/>
+      <c r="C25" s="152" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="154"/>
       <c r="G25" s="60"/>
       <c r="H25" s="63">
         <v>5</v>
@@ -5198,7 +5198,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" s="73"/>
       <c r="E27" s="73"/>
@@ -5208,7 +5208,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="216" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J27" s="217"/>
       <c r="K27" s="217"/>
@@ -5222,17 +5222,17 @@
       <c r="C28" s="75"/>
       <c r="D28" s="76"/>
       <c r="E28" s="76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F28" s="77"/>
       <c r="G28" s="33"/>
       <c r="H28" s="27">
         <v>5</v>
       </c>
-      <c r="I28" s="152"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="154"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="156"/>
+      <c r="L28" s="157"/>
     </row>
     <row r="29" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="34"/>
@@ -5241,10 +5241,10 @@
       </c>
       <c r="C29" s="205"/>
       <c r="D29" s="206"/>
-      <c r="E29" s="156" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="157"/>
+      <c r="E29" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="94"/>
       <c r="G29" s="34"/>
       <c r="H29" s="29">
         <v>6</v>
@@ -5271,10 +5271,10 @@
       <c r="H30" s="31">
         <v>2</v>
       </c>
-      <c r="I30" s="115"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="116"/>
-      <c r="L30" s="117"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="122"/>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="37"/>
@@ -5282,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" s="73"/>
       <c r="E31" s="73"/>
@@ -5292,7 +5292,7 @@
         <v>3</v>
       </c>
       <c r="I31" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J31" s="73"/>
       <c r="K31" s="73"/>
@@ -5303,18 +5303,18 @@
       <c r="B32" s="43">
         <v>4</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="105"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="44"/>
       <c r="H32" s="43">
         <v>4</v>
       </c>
-      <c r="I32" s="103"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="105"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="110"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="48"/>
@@ -5411,13 +5411,13 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -5625,7 +5625,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="270" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" s="270"/>
       <c r="E9" s="17"/>
@@ -5652,10 +5652,10 @@
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="145"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="151"/>
     </row>
     <row r="12" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
@@ -5663,7 +5663,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" s="73"/>
       <c r="E12" s="73"/>
@@ -5675,7 +5675,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="271" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="272"/>
       <c r="E13" s="272"/>
@@ -5754,10 +5754,10 @@
       <c r="B20" s="27">
         <v>4</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="115"/>
       <c r="E20" s="73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="74"/>
     </row>
@@ -5767,7 +5767,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" s="76"/>
       <c r="E21" s="73" t="s">
@@ -5780,8 +5780,8 @@
       <c r="B22" s="27">
         <v>6</v>
       </c>
-      <c r="C22" s="103"/>
-      <c r="D22" s="104"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
       <c r="E22" s="73" t="s">
         <v>77</v>
       </c>
@@ -5794,14 +5794,14 @@
       <c r="B23" s="31">
         <v>1</v>
       </c>
-      <c r="C23" s="146" t="s">
+      <c r="C23" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="147"/>
-      <c r="E23" s="101" t="s">
-        <v>132</v>
-      </c>
-      <c r="F23" s="102"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="106" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="107"/>
     </row>
     <row r="24" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D24" s="73"/>
       <c r="E24" s="76" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F24" s="77"/>
     </row>
@@ -5823,7 +5823,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" s="73"/>
       <c r="E25" s="73"/>
@@ -5847,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="274"/>
       <c r="E27" s="275"/>
@@ -5858,8 +5858,8 @@
       <c r="B28" s="27">
         <v>2</v>
       </c>
-      <c r="C28" s="131" t="s">
-        <v>128</v>
+      <c r="C28" s="138" t="s">
+        <v>127</v>
       </c>
       <c r="D28" s="182"/>
       <c r="E28" s="276"/>
@@ -5870,12 +5870,12 @@
       <c r="B29" s="27">
         <v>3</v>
       </c>
-      <c r="C29" s="131" t="s">
+      <c r="C29" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="133"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="140"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="34"/>
@@ -5934,7 +5934,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
